--- a/reports/next_day_forecast.xlsx
+++ b/reports/next_day_forecast.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,6 +456,16 @@
           <t>TrainSize</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>OutliersProcessed</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OutliersPercent</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -482,6 +492,12 @@
       </c>
       <c r="G2" t="n">
         <v>1103</v>
+      </c>
+      <c r="H2" t="n">
+        <v>60</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.439709882139619</v>
       </c>
     </row>
   </sheetData>
